--- a/medicine_list.xlsx
+++ b/medicine_list.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,752 +454,1183 @@
           <t>Stock</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Pack Type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Pack Qty</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALSITA MP 500</t>
+          <t>ACC-CHECK INSTANT FOR W GLUCOMETER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25443008</t>
+          <t>91800097</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>02/2028</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>203</v>
+        <v>1450</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMLOKIND-5</t>
+          <t>ACCU-CHECK INSTANT GLUCOSTRIP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G55Y031</t>
+          <t>303837</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>03/2027</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>1115</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bottle of 50</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AZTOR 10 (1*15)</t>
+          <t>ACCU-CHECK INSTANT'SS COMBO( GLUCOMETER+ STRIP OF 10)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GTG1406A</t>
+          <t>92200173</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>03/2028</t>
+          <t>04/2028</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>820</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AZTOR 20 (1*15)</t>
+          <t>ALSITA MP 500</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GTG1792A</t>
+          <t>25443008</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>05/2028</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>201</v>
+        <v>19.075</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>10</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AZTOR 20 MG TAB</t>
+          <t>ALSITA MP 500</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GTG1449B</t>
+          <t>25444213</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>214</v>
+        <v>19.075</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>70</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BD ULTRA FINE PEN NEEDLES 4mm 32 G</t>
+          <t>AMLOKIND-5MG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>*****</t>
+          <t>G55Y031</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>05/2028</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>100</v>
+        <v>1.578</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BILASURE-M</t>
+          <t>AZTOR 20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AXC0127</t>
+          <t>GTG1449B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>04/2028</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>227</v>
+        <v>13.406</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRO-ZEDEX SF</t>
+          <t>AZTOR-10 MG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D250602</t>
+          <t>GTG1406A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>03/2028</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>5.3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRO-ZEDEX SF</t>
+          <t>AZTOR-10 MG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D250602</t>
+          <t>GTG3646A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03/2027</t>
+          <t>10/2028</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>5.3</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>135</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CABGOLIN-0.25</t>
+          <t>AZTOR-20 MG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GTG2721A</t>
+          <t>GTG1792A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>05/2028</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>252</v>
+        <v>13.406</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>150</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CABGOLIN-0.5</t>
+          <t>BASUGINE 3ML CATRIDGE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GTG1713A</t>
+          <t>122509141</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>08/2028</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>549</v>
+        <v>651.95</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CANDID B CREAM 20G</t>
+          <t>BASUGINE DESPOSABLE PEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11251184</t>
+          <t>122506012D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>05/2028</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>782.35</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CIPLAR 10</t>
+          <t>BILASURE-M</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5SB0676</t>
+          <t>AXC0127</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>21.28</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>110</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CIPLAR LA-20</t>
+          <t>BRO-ZEDEX SF COUGH SYP SF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5SB0745</t>
+          <t>D250602</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>187.68</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DISPOVAN 32G PEN NEEDLES</t>
+          <t>CABGOLIN 0.25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>544N</t>
+          <t>GTG2721A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01/2030</t>
+          <t>04/2027</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>63.047</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Strip of 4</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DISPOVAN 32G PEN NEEDLES</t>
+          <t>CABGOLIN 0.5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>317B</t>
+          <t>GTG1713A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>04/2027</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>128.672</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Strip of 4</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUXRAB-D CAP 1*10 </t>
+          <t>CALCITAS D3 LIQUID 5 ML</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CPC-25237</t>
+          <t>OBIK2519</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>04/2027</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>150</v>
+        <v>78.28</v>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>208</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ECONORM SACHET</t>
+          <t>CANDID B CREAM 20 GM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>11251184</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69</v>
+        <v>178.12</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tube</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tube of 1</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ECOSPRIN AV 75 CAP</t>
+          <t>CIPLAR-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28027356</t>
+          <t>5SB0676</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2028</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>62</v>
+        <v>1.396</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>135</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ECOSPRIN AV 75/20 CAP</t>
+          <t>CIPLAR-LA 20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28027374</t>
+          <t>5SB0745</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>4.29</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>60</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EMPANEO L 25</t>
+          <t>DUXFOL-D</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>N2502371</t>
+          <t>G130995A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>139</v>
+        <v>17.5</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>360</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EMPHA L 25</t>
+          <t>DUXRAB-D CAPSULE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>N2502241</t>
+          <t>CPC-25237</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>02/2027</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>139</v>
+        <v>14.062</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>420</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EMPHA M 12.5/500</t>
+          <t>ECONORM SACHET</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>N2500670</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>109</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sachet</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sachet of 1</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EMPHA M 12.5/500</t>
+          <t>ECOSPRIN AV 75 CAP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>N2501438</t>
+          <t>28027356</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>03/2027</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>109</v>
+        <v>4.0813</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>180</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EPLEHEF 25 MG</t>
+          <t>ECOSPRIN AV 75/20 CAP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BRF09102A</t>
+          <t>28027374</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>08/2028</t>
+          <t>03/2027</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>246</v>
+        <v>4.4533</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>180</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EPLEHEF 50 MG 1*10</t>
+          <t>EMPANEO L 25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BRF09103A</t>
+          <t>N2502371</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>09/2028</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>388</v>
+        <v>13.031</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EVALON CREAM 15 GM</t>
+          <t>EMPHA L 25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B01325C</t>
+          <t>N2502241</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>02/2028</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>524</v>
+        <v>13.03</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>110</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EVION-LC</t>
+          <t>EMPHA M 12.5/500</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5268C82301</t>
+          <t>N2500670</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>02/2027</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>65</v>
+        <v>10.21</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FERISOME TAB</t>
+          <t>EMPHA M 12.5/500</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FRSMGC020</t>
+          <t>N2501438</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>05/2027</t>
+          <t>03/2027</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>348</v>
+        <v>10.219</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>60</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FOLIGRAF 1200 IU 8ML (2 ML MULTIDOSE PEN)</t>
+          <t>EPLEHEF 25 MG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B25125018</t>
+          <t>BRF09102A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>08/2028</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>34688</v>
+        <v>24.56</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GEMER 0.5 MG TAB</t>
+          <t>EPLEHEF 50MG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GTG3369A</t>
+          <t>BRF09103A</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>08/2028</t>
         </is>
       </c>
       <c r="D32" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="E32" t="n">
         <v>40</v>
       </c>
-      <c r="E32" t="n">
-        <v>13</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GEMER 1 TAB</t>
+          <t>EVALON CREAM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GTG3066A</t>
+          <t>B01325C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>02/2028</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>167</v>
+        <v>524.05</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tube</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Tube of 1</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEMER 2 </t>
+          <t>EVION-LC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GTG3179A</t>
+          <t>5244C8230</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1208,573 +1639,898 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>237</v>
+        <v>6.45</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GEMER 2 TAB</t>
+          <t>EVION-LC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GTG3180A</t>
+          <t>5268C8230</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>02/2027</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>237</v>
+        <v>6.45</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GINETTE 35</t>
+          <t>FERISOME-TAB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>25S2HTA663</t>
+          <t>FRSMGC020</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>05/2027</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>478</v>
+        <v>20.64</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GLIMISAVE MV 1</t>
+          <t>FOLIGRAF 1200 IU8ML CART</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AGMA25002</t>
+          <t>BB25125018</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>269</v>
+        <v>34687.5</v>
       </c>
       <c r="E37" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLIMISAVE MV 2 </t>
+          <t>FOLIGRAF 1200 IU8ML CART</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GGMV25004</t>
+          <t>B25125018</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>327</v>
+        <v>34687.5</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GLIZID  XR 60 MG TAB</t>
+          <t>GEMER-0.5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>T45Y005</t>
+          <t>GTG3369A</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>118</v>
+        <v>3.9</v>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GLIZID 40 MG TAB</t>
+          <t>GEMER-1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R35Y004</t>
+          <t>GTG3066A</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>36</v>
+        <v>11.187</v>
       </c>
       <c r="E40" t="n">
-        <v>9</v>
+        <v>45</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>15</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GLIZID M XR 30 MG TAB</t>
+          <t>GEMER-1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>V2FZY013</t>
+          <t>GTG3495A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>98</v>
+        <v>11.187</v>
       </c>
       <c r="E41" t="n">
-        <v>11</v>
+        <v>150</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>15</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GLIZID M XR 60 MG TAB</t>
+          <t>GEMER-2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>V3FZY024</t>
+          <t>GTG3180A</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>147</v>
+        <v>15.812</v>
       </c>
       <c r="E42" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>15</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GLIZID XR 30 MG TAB</t>
+          <t>GEMER-2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>T35Y001</t>
+          <t>GTG3038A</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>70</v>
+        <v>15.812</v>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>135</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>15</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GLYCOMET SR 500 MG</t>
+          <t>GEMER-2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>60002333</t>
+          <t>GTG3179A</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>42</v>
+        <v>15.812</v>
       </c>
       <c r="E44" t="n">
-        <v>19</v>
+        <v>150</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>15</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HUCOG 2000HP LIQ</t>
+          <t>GINETTE 35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B10725001</t>
+          <t>25S2HTA53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>05/2027</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>367</v>
+        <v>478.4</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Strip of 1</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>INSUCRAFT SUS.</t>
+          <t>GLIMISAVE-MV-1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LLD-8791B</t>
+          <t>AGMA25002</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>05/2028</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>200</v>
+        <v>16.85</v>
       </c>
       <c r="E46" t="n">
-        <v>18</v>
+        <v>105</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>15</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>INSULIN SYRINGE 100U</t>
+          <t>GLIMISAVE-MV-2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4310210</t>
+          <t>GGMV25004</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>12/2029</t>
+          <t>05/2028</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>20.47</v>
       </c>
       <c r="E47" t="n">
-        <v>20</v>
+        <v>90</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>15</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>INSULIN SYRINGE-BD U40 1*1</t>
+          <t>GLIMISAVE-MV-2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5013013</t>
+          <t>AGMV25007</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/2030</t>
+          <t>11/2028</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>22.516</v>
       </c>
       <c r="E48" t="n">
-        <v>20</v>
+        <v>165</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ISTAVEL EMPA 25 MG</t>
+          <t>GLIZID-40MG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AXC0026</t>
+          <t>R35Y004</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2028</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>220</v>
+        <v>3.529</v>
       </c>
       <c r="E49" t="n">
+        <v>90</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
         <v>10</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JUSLINA 5 MG TAB 1*10</t>
+          <t>GLIZID-M-XR-30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B5OAY006</t>
+          <t>V2FY013</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>77</v>
+        <v>9.186999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>16</v>
+        <v>110</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>10</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUSLINA M 2.5/500 </t>
+          <t>GLIZID-M-XR-60</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B60AY003</t>
+          <t>V3FZY024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>77</v>
+        <v>13.848</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>80</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>10</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JUSLINA M 2.5/500 MG TAB</t>
+          <t>GLIZID-XR-30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B6OAY004</t>
+          <t>T35Y001</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>02/2028</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>81</v>
+        <v>6.484</v>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>80</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>10</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MEPRATE TAB</t>
+          <t>GLIZID-XR-60</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CUE18AEA</t>
+          <t>T454005</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>04/2028</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>67</v>
+        <v>11.127</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>80</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>10</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MOUNJARO 15 MG KWIKPEN</t>
+          <t>GLYCOMET SR-500MG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>D938367</t>
+          <t>60002333</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>09/2028</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>25781</v>
+        <v>2.098</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>280</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>20</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Strip of 20</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MOUNJARO 2.5 MG KWIKPEN</t>
+          <t>HUCOG 200HP LIQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>D912974</t>
+          <t>B10725001</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>04/2027</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13125</v>
+        <v>367.1</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MOUNJARO 5 MG KWIKPEN</t>
+          <t>INSUCRAFT SUSPENSION</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>D919450</t>
+          <t>LLD-8791</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>16406</v>
+        <v>187.5</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MOX CV 625MG</t>
+          <t>INSULIN SYRING-40IU-BD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BYC0051</t>
+          <t>5013013</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>01/2030</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>209</v>
+        <v>10.55</v>
       </c>
       <c r="E57" t="n">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NAXDOM-500</t>
+          <t>INSULIN SYRING-IU100-BD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FHC0946</t>
+          <t>4310210</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>12/2029</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>176</v>
+        <v>9.66</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>20</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NEOGADINE ELEXIR LIQ</t>
+          <t>ISTAVEL EMPHA 25 MG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BO2K25098</t>
+          <t>AXC0026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1783,1528 +2539,3515 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>234</v>
+        <v>20.62</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>10</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NUROKIND LC</t>
+          <t>JUSLINA M 2.5/500 MG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B95Y128</t>
+          <t>B6OAY4004</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>239</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>10</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NUROKIND-LC</t>
+          <t>JUSLINA M 2.5/500 MG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>b95y125</t>
+          <t>B6OAY004</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>238</v>
+        <v>7.142</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>10</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OLKEM 20</t>
+          <t>JUSLINA-5 MG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>25443043</t>
+          <t>B5OAY006</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>243</v>
+        <v>7.663</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>160</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>10</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OLKEM 20 AM</t>
+          <t>LINARES-M</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>25490463</t>
+          <t>ALNN25011</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>292</v>
+        <v>11.33</v>
       </c>
       <c r="E63" t="n">
-        <v>13</v>
+        <v>110</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OLKEM TRIO 6.25 MG</t>
+          <t>MEPRATE-10 MG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OTS25008SS</t>
+          <t>CUE04AEA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>08/2028</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>209</v>
+        <v>4.441</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>30</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>10</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OLMEZEST 20 TAB</t>
+          <t>MONJARO 15 MG KWIK PEN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SIG1899C</t>
+          <t>D938367</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>150</v>
+        <v>25781</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLMEZEST AM </t>
+          <t>MONJARO 2.5 MG KWIK PEN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SIG1951A</t>
+          <t>D912974</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>05/2027</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>195</v>
+        <v>13125</v>
       </c>
       <c r="E66" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ONDEM MD 4</t>
+          <t>MONJARO 5 MG KWIK PEN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>25442254</t>
+          <t>D919450</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>05/2027</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>59</v>
+        <v>16406.25</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ONDERO D 10 TAB</t>
+          <t>MONJARO 5 MG KWIK PEN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EMV252581A</t>
+          <t>D928027</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>221</v>
+        <v>16406.25</v>
       </c>
       <c r="E68" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ONDERO DM 500 TAB</t>
+          <t>MOX-CV-625</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GT251469</t>
+          <t>BYC0051</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>01/2027</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>230</v>
+        <v>19.53</v>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>170</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>10</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OVARAL L TAB</t>
+          <t>NAXDOM-500</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MR6546</t>
+          <t>FHC0946</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>09/2028</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>68</v>
+        <v>11.75</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>120</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>15</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OXRAMET S XR 10/100/500 1*7</t>
+          <t>NEOGADINE ELIXIR SYP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GTG3613A</t>
+          <t>B02K25098</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>12/2027</t>
+          <t>01/2027</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>149</v>
+        <v>233.5</v>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PIOZ 15 TAB</t>
+          <t>NOVOFINE NEEDLE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>48020714</t>
+          <t>544N</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>09/2030</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="E72" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PIOZ MF-15 TAB</t>
+          <t>NOVOFINE NEEDLE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>28027440</t>
+          <t>317B</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>03/2028</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>145</v>
+        <v>13.13</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>4</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ROSUVAS 10 MG TAB</t>
+          <t>NOVOFINE NEEDLE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIG1644A</t>
+          <t>523F</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>05/2030</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>346</v>
+        <v>14</v>
       </c>
       <c r="E74" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ROSUVAS 5 MG TAB</t>
+          <t>NOVOFINE NEEDLE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SIG1784A</t>
+          <t>012477</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>05/2029</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>210</v>
+        <v>6.09</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SHELCAL 500 TAB</t>
+          <t>NUROKIND-LC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8LV2M362</t>
+          <t>B95Y132</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>159</v>
+        <v>15.927</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>15</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SHELCAL 500 TAB</t>
+          <t>NUROKIND-LC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8LV2M349</t>
+          <t>B95Y125</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>159</v>
+        <v>15.927</v>
       </c>
       <c r="E77" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>15</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SHELCAL CT TAB</t>
+          <t>NUROKIND-LC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GAXF0023</t>
+          <t>B95Y128</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>404</v>
+        <v>15.927</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>15</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SITARA M 100/500</t>
+          <t>OLKEM 20</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EMV252758C</t>
+          <t>25443043</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>164</v>
+        <v>22.78</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>10</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SITARA M 100/500</t>
+          <t>OLKEM 20</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EMV252762A</t>
+          <t>25444565</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>11/2027</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>164</v>
+        <v>15.186</v>
       </c>
       <c r="E80" t="n">
-        <v>7</v>
+        <v>300</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>15</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SITARA M 50/500</t>
+          <t>OLKEM AM 20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EMV252263</t>
+          <t>25490463</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>04/2027</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>185</v>
+        <v>27.42</v>
       </c>
       <c r="E81" t="n">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>10</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SITARED M  50/500 MG TAB</t>
+          <t>OLKEM AM 20</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SIG2194A</t>
+          <t>25490707</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>177</v>
+        <v>27.42</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>10</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SITARED M  50/500 MG TAB</t>
+          <t>OLKEM TRIO 6.25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SIG2272B</t>
+          <t>OTS25008SS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>177</v>
+        <v>19.59</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>10</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SITARED M XR 100/1000 MG TAB (1*10)</t>
+          <t>OLMEZEST 20</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GTF1664B</t>
+          <t>SIG899C</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>02/2027</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>60</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>10</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SITARED M XR 100/500 MG TAB</t>
+          <t>OLMEZEST AM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AXC0097</t>
+          <t>SIG1951A</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>216</v>
+        <v>19.5</v>
       </c>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>100</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>10</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SPORLAC-DS</t>
+          <t>ONDEM-MD-4MG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BDS25019</t>
+          <t>25442254</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>05/2027</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>239</v>
+        <v>5.48</v>
       </c>
       <c r="E86" t="n">
-        <v>29</v>
+        <v>360</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>10</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STEMETIL MD (1*15)</t>
+          <t>ONDERO D10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SEA25022</t>
+          <t>EMV252581A</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>190</v>
+        <v>22.12</v>
       </c>
       <c r="E87" t="n">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>10</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SYSCAN-150 MG 1*1</t>
+          <t>ONDERO DM 500</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CBD2M001</t>
+          <t>GT251469</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>20</v>
+        <v>21.55</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>10</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>T BACT OINTMENT 5GM</t>
+          <t>OVRAL-L TAB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>K73K</t>
+          <t>MR6546</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>01/2027</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>115</v>
+        <v>3.221</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>63</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>21</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Strip of 21</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TELMIKIND TRIO 6.25 TAB</t>
+          <t>OXRAMET S XR 10/100/500</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>A6OAY022</t>
+          <t>GTG3150A</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>132</v>
+        <v>22.294</v>
       </c>
       <c r="E90" t="n">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>7</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Strip of 7</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TELVOK 40 MG</t>
+          <t>OXRAMET S XR 10/100/500</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AT2511142</t>
+          <t>GTG3613A</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>71</v>
+        <v>21.294</v>
       </c>
       <c r="E91" t="n">
-        <v>12</v>
+        <v>28</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>7</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Strip of 7</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>THYRONORM 100 MCG</t>
+          <t>OZEMPIC 0.25 MG PEN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TMH25258</t>
+          <t>RP5V726</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>11/2027</t>
+          <t>07/2028</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>169</v>
+        <v>8800</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>THYRONORM 100 MCG</t>
+          <t>PEN NEEDLE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TMH25217</t>
+          <t>5056002</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>02/2030</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>180</v>
+        <v>20.25</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>THYRONORM 112 MCG</t>
+          <t>PIOZ 15MG TAB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EBRH5005</t>
+          <t>48020714</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>11/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>213</v>
+        <v>78.52</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>10</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>THYRONORM 12.5 MCG</t>
+          <t>PIOZ MF-15 TAB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AEL0477</t>
+          <t>28027440</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>190</v>
+        <v>14.592</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>160</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>10</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>THYRONORM 125 MCG</t>
+          <t>ROSUVAS 10</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EBRI5008</t>
+          <t>SIG1644A</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>01/2028</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>216</v>
+        <v>23.062</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>15</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>THYRONORM 25 MCG</t>
+          <t>ROSUVAS 5</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TMB25278</t>
+          <t>SIG1784A</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>01/2028</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>186</v>
+        <v>13.125</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>15</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>THYRONORM 25 MCG</t>
+          <t>SHELCAL-500</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TMB25292</t>
+          <t>8LV2M362</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>186</v>
+        <v>9.91</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>15</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>THYRONORM 37.5 MCG</t>
+          <t>SHELCAL-500</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TMC25063*</t>
+          <t>8LV2M447</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>188</v>
+        <v>10.89</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>120</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>15</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>THYRONORM 50 MCG</t>
+          <t>SHELCAL-500</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TMD25396*</t>
+          <t>8LVM349</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>132</v>
+        <v>9.912000000000001</v>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>15</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>THYRONORM 62.5 MCG</t>
+          <t>SHELCAL-CT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EBRF5036*</t>
+          <t>GAXF0023</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>220</v>
+        <v>25.28</v>
       </c>
       <c r="E101" t="n">
-        <v>3</v>
+        <v>75</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>15</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>THYRONORM 75 MCG</t>
+          <t>SHELCAL-XT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TMF25182*</t>
+          <t>2SG6M104</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>184</v>
+        <v>26.81</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>15</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>THYRONORM 75 MCG</t>
+          <t>SITARA M 100\500</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TMF25209</t>
+          <t>EMV252758C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>184</v>
+        <v>16.383</v>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>10</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>THYRONORM 75 MCG</t>
+          <t>SITARA M 100\500</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TMF25231</t>
+          <t>EMV252762</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>184</v>
+        <v>16.383</v>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>10</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>THYRONORM 88 MCG</t>
+          <t>SITARA M 50/500</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EBRG5028*</t>
+          <t>EMV252263</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>211</v>
+        <v>18.422</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>10</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>THYRONORM 88 MCG</t>
+          <t>SITARED M 50/500</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EBRG5036</t>
+          <t>SIG2194A</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>211</v>
+        <v>11.75</v>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>15</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TRIGLYNASE 1 TAB</t>
+          <t>SITARED M 50/500</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>28027170</t>
+          <t>SIG2272B</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>02/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>94</v>
+        <v>11.75</v>
       </c>
       <c r="E107" t="n">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>15</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRIGLYNASE 2 </t>
+          <t>SITARED M XR 100/1000</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>28027306</t>
+          <t>GTF1664B</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>94</v>
+        <v>14.906</v>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>20</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>10</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TRIGLYNASE 2 TAB</t>
+          <t>SITARED M XR 100/500</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>28027385</t>
+          <t>AXC0097</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>94</v>
+        <v>13.5</v>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>15</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TRIOLMEZEST 20 TAB</t>
+          <t>SPORLAC-DS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GTG2880A</t>
+          <t>BDS25019</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>218</v>
+        <v>8.965999999999999</v>
       </c>
       <c r="E110" t="n">
-        <v>9</v>
+        <v>600</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>25</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Strip of 25</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TRYPTOMER-10</t>
+          <t>STEMETIL-MD TAB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>D2500387</t>
+          <t>SEA25022</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>77</v>
+        <v>11.87</v>
       </c>
       <c r="E111" t="n">
-        <v>4</v>
+        <v>279</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>15</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ULTRAFINE NEEDLE NANO 1*1</t>
+          <t>SYSCAN-150</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5056002</t>
+          <t>CBD2M001</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>02/2030</t>
+          <t>01/2028</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>20</v>
+        <v>20.17</v>
       </c>
       <c r="E112" t="n">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Strip of 1</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VSL-3 CAP</t>
+          <t>T-BACT OINT 5GM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JMG1096A</t>
+          <t>K73K</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>452</v>
+        <v>108.36</v>
       </c>
       <c r="E113" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tube</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Tube of 1</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>WONRIDE M 1 TAB</t>
+          <t>TELMEKIND-TRIO 6.25 TAB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WNM1325004</t>
+          <t>A6OAY022</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>121</v>
+        <v>12.454</v>
       </c>
       <c r="E114" t="n">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>10</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>WONRIDE M 2 TAB</t>
+          <t>TELVOK-40 MG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WOH25004</t>
+          <t>ATH2511142</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>129</v>
+        <v>7.097</v>
       </c>
       <c r="E115" t="n">
-        <v>7</v>
+        <v>20</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>10</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>XGLAR REFILL</t>
+          <t>THYRONORM 100</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>C24IGH4010</t>
+          <t>TMH25237</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>640</v>
+        <v>168.82</v>
       </c>
       <c r="E116" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>XSULIN R CART</t>
+          <t>THYRONORM 100</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TBB030225</t>
+          <t>TMN25217</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>375</v>
+        <v>168.82</v>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>XSULIN R VIAL</t>
+          <t>THYRONORM 100</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>A032515016</t>
+          <t>TMH25258</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>04/2027</t>
+          <t>11/2027</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>181</v>
+        <v>168.82</v>
       </c>
       <c r="E118" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>YURPEAK (TIRZEPATIDE) 2.5 MG KWIKPEN INJECTION 1*1</t>
+          <t>THYRONORM 112</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>D921081</t>
+          <t>TMI25008*</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>13125</v>
+        <v>212.72</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEDEX SF </t>
+          <t>THYRONORM 112</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>D250570</t>
+          <t>EBRH5005</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>11/2027</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>190</v>
+        <v>251.7</v>
       </c>
       <c r="E120" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ZERODOL-P</t>
+          <t>THYRONORM 12.5</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KVB0125117AS</t>
+          <t>AEL0406*</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>76</v>
+        <v>189.72</v>
       </c>
       <c r="E121" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ZERODOL-SP</t>
+          <t>THYRONORM 12.5</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FND0825044AK</t>
+          <t>AEL0477</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>140</v>
+        <v>189.72</v>
       </c>
       <c r="E122" t="n">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ZINCOVIT</t>
+          <t>THYRONORM 125</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ZVT25220</t>
+          <t>EBRI5008</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>108</v>
+        <v>216.63</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ZINCOVIT</t>
+          <t>THYRONORM 125</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ZVT25220</t>
+          <t>EBRI5023</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>108</v>
+        <v>216.63</v>
       </c>
       <c r="E124" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>punit</t>
+          <t>THYRONORM 25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>hiujndfsi</t>
+          <t>TMB25278</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>300</v>
+        <v>185.4</v>
       </c>
       <c r="E125" t="n">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>THYRONORM 25</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TMB25292</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>10/2027</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>THYRONORM 37.5</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TMC25063*</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>08/2027</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>187.85</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>THYRONORM 50</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>TMD25396*</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>10/2027</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>132.02</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>THYRONORM 50</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>TMD25396</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>10/2027</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>132.02</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>THYRONORM 62.5</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EBRG5028*</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>08/2027</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>206.37</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>THYRONORM 62.5</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EBRF5036</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>07/2027</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>206.37</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>THYRONORM 75</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TMF25182*</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>08/2027</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>183.97</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>THYRONORM 75</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TMF25231</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>10/2027</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>183.97</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>THYRONORM 75</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>TMF25209</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>10/2027</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>183.97</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>THYRONORM 88</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EBRG5028*</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>08/2027</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>211.27</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>THYRONORM 88</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>EBRG5036</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>09/2027</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>211.28</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TRIGLYNASE-1</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>28027170</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>02/2027</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>6.422</v>
+      </c>
+      <c r="E137" t="n">
+        <v>130</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>10</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>TRIGLYNASE-2</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>28027385</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>04/2027</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>9.352</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>10</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TRIGLYNASE-2</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>28027306</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>03/2027</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>9.352</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>10</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>TRIOLMEZEST 40 MG</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>GTC2880A</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>08/2027</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>21.844</v>
+      </c>
+      <c r="E140" t="n">
+        <v>80</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>10</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>TRYPTOMER-10 MG</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D2500387</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>10/2027</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="E141" t="n">
+        <v>595</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>30</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Strip of 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>VSL 3 CAP</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>JMG1096A</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>09/2027</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="E142" t="n">
+        <v>20</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>10</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>WONRIDE-M1</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>WNM1325004</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>07/2027</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>7.562</v>
+      </c>
+      <c r="E143" t="n">
+        <v>45</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>15</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>WONRIDE-M1</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>WNM1325005</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>11/2027</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>7.562</v>
+      </c>
+      <c r="E144" t="n">
+        <v>180</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>15</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>WONRIDE-M2</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>WOH25004</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>09/2027</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>8.593999999999999</v>
+      </c>
+      <c r="E145" t="n">
+        <v>15</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>15</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>WONRIDE-M2</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>WOH25005</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>11/2027</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>8.593999999999999</v>
+      </c>
+      <c r="E146" t="n">
+        <v>180</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>15</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>XGLAR CART</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>C241GH4010</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>06/2027</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>640.8</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>XSULIN R CART</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>TBB030225</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>01/2028</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>175.1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>XSULIN R CART</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>A042517604</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>07/2028</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>375.1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>9</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>XSULIN R VIAL</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>A032515016</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>04/2027</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>181.39</v>
+      </c>
+      <c r="E150" t="n">
+        <v>5</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>YURPEAK 2.5MG/0.6ML PEN</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D921081</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>05/2027</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>13125</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Unit of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ZEDEX-SF COUGH SYP</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D250569</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>09/2027</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>190.31</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ZEDEX-SF COUGH SYP</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D250570</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>09/2027</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>190.31</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Bottle of 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ZERODOL-P</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>KVB012511</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>08/2027</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="E154" t="n">
+        <v>50</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>10</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ZERODOL-SP</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>FND082504</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>03/2028</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="E155" t="n">
+        <v>80</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>10</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ZINCOVIT TAB</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ZVT25220</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>02/2027</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>7.179</v>
+      </c>
+      <c r="E156" t="n">
+        <v>150</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>15</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Strip of 15</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/medicine_list.xlsx
+++ b/medicine_list.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2813,21 +2813,21 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MONJARO 5 MG KWIK PEN</t>
+          <t>MONJARO 2.5 MG KWIK PEN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>D919450</t>
+          <t>D924668</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>05/2027</t>
+          <t>01/2027</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16406.25</v>
+        <v>13125</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>D928027</t>
+          <t>D919450</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>05/2027</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2885,60 +2885,60 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MOX-CV-625</t>
+          <t>MONJARO 5 MG KWIK PEN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BYC0051</t>
+          <t>D928027</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>19.53</v>
+        <v>16406.25</v>
       </c>
       <c r="E69" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Unit of 1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NAXDOM-500</t>
+          <t>MOX-CV-625</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FHC0946</t>
+          <t>BYC0051</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>09/2028</t>
+          <t>01/2027</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.75</v>
+        <v>19.53</v>
       </c>
       <c r="E70" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2946,75 +2946,75 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Strip of 15</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NEOGADINE ELIXIR SYP</t>
+          <t>NAXDOM-500</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B02K25098</t>
+          <t>FHC0946</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>09/2028</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>233.5</v>
+        <v>11.75</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bottle</t>
+          <t>Strip</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bottle of 1</t>
+          <t>Strip of 15</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NOVOFINE NEEDLE</t>
+          <t>NEOGADINE ELIXIR SYP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>544N</t>
+          <t>B02K25098</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>09/2030</t>
+          <t>01/2027</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>14</v>
+        <v>233.5</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Bottle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Unit of 1</t>
+          <t>Bottle of 1</t>
         </is>
       </c>
     </row>
@@ -3034,19 +3034,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>317B</t>
+          <t>544N</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>03/2028</t>
+          <t>09/2030</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.13</v>
+        <v>14</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3070,19 +3070,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>523F</t>
+          <t>317B</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>05/2030</t>
+          <t>03/2028</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14</v>
+        <v>13.13</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3106,16 +3106,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>012477</t>
+          <t>523F</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>05/2029</t>
+          <t>05/2030</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6.09</v>
+        <v>14</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -3137,36 +3137,36 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NUROKIND-LC</t>
+          <t>NOVOFINE NEEDLE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B95Y132</t>
+          <t>012477</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>05/2029</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>15.927</v>
+        <v>6.09</v>
       </c>
       <c r="E76" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Strip of 15</t>
+          <t>Unit of 1</t>
         </is>
       </c>
     </row>
@@ -3178,19 +3178,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B95Y125</t>
+          <t>B95Y132</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>15.927</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B95Y128</t>
+          <t>B95Y125</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3245,24 +3245,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OLKEM 20</t>
+          <t>NUROKIND-LC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>25443043</t>
+          <t>B95Y128</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>22.78</v>
+        <v>15.927</v>
       </c>
       <c r="E79" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3270,11 +3270,11 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Strip of 15</t>
         </is>
       </c>
     </row>
@@ -3286,19 +3286,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>25444565</t>
+          <t>25443043</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>11/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>15.186</v>
+        <v>22.78</v>
       </c>
       <c r="E80" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3306,35 +3306,35 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Strip of 15</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OLKEM AM 20</t>
+          <t>OLKEM 20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>25490463</t>
+          <t>25444565</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>04/2027</t>
+          <t>11/2027</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>27.42</v>
+        <v>15.186</v>
       </c>
       <c r="E81" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3342,11 +3342,11 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Strip of 15</t>
         </is>
       </c>
     </row>
@@ -3358,19 +3358,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>25490707</t>
+          <t>25490463</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>04/2027</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>27.42</v>
       </c>
       <c r="E82" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3389,24 +3389,24 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OLKEM TRIO 6.25</t>
+          <t>OLKEM AM 20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OTS25008SS</t>
+          <t>25490707</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>19.59</v>
+        <v>27.42</v>
       </c>
       <c r="E83" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3425,24 +3425,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OLMEZEST 20</t>
+          <t>OLKEM TRIO 6.25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SIG899C</t>
+          <t>OTS25008SS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>02/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>15</v>
+        <v>19.59</v>
       </c>
       <c r="E84" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3461,24 +3461,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OLMEZEST AM</t>
+          <t>OLMEZEST 20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SIG1951A</t>
+          <t>SIG899C</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>02/2027</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="E85" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3497,24 +3497,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ONDEM-MD-4MG</t>
+          <t>OLMEZEST AM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>25442254</t>
+          <t>SIG1951A</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>05/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5.48</v>
+        <v>19.5</v>
       </c>
       <c r="E86" t="n">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3533,24 +3533,24 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ONDERO D10</t>
+          <t>ONDEM-MD-4MG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EMV252581A</t>
+          <t>25442254</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>05/2027</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>22.12</v>
+        <v>5.48</v>
       </c>
       <c r="E87" t="n">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3569,24 +3569,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ONDERO DM 500</t>
+          <t>ONDERO D10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GT251469</t>
+          <t>EMV252581A</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21.55</v>
+        <v>22.12</v>
       </c>
       <c r="E88" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3605,24 +3605,24 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OVRAL-L TAB</t>
+          <t>ONDERO DM 500</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MR6546</t>
+          <t>GT251469</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>01/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3.221</v>
+        <v>21.55</v>
       </c>
       <c r="E89" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3630,35 +3630,35 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Strip of 21</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OXRAMET S XR 10/100/500</t>
+          <t>OVRAL-L TAB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GTG3150A</t>
+          <t>MR6546</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>01/2027</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>22.294</v>
+        <v>3.221</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3666,11 +3666,11 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Strip of 7</t>
+          <t>Strip of 21</t>
         </is>
       </c>
     </row>
@@ -3682,19 +3682,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GTG3613A</t>
+          <t>GTG3150A</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>21.294</v>
+        <v>22.294</v>
       </c>
       <c r="E91" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3713,60 +3713,60 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OZEMPIC 0.25 MG PEN</t>
+          <t>OXRAMET S XR 10/100/500</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RP5V726</t>
+          <t>GTG3613A</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>07/2028</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>8800</v>
+        <v>21.294</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Strip</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Unit of 1</t>
+          <t>Strip of 7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PEN NEEDLE</t>
+          <t>OZEMPIC 0.25 MG PEN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5056002</t>
+          <t>RP5V726</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>02/2030</t>
+          <t>07/2028</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>20.25</v>
+        <v>8800</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3785,96 +3785,96 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PIOZ 15MG TAB</t>
+          <t>PEN NEEDLE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>48020714</t>
+          <t>5056002</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>02/2030</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>78.52</v>
+        <v>20.25</v>
       </c>
       <c r="E94" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Unit of 1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PIOZ MF-15 TAB</t>
+          <t>PEN NEEDLE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>28027440</t>
+          <t>317B</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>01/2028</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>14.592</v>
+        <v>13.13</v>
       </c>
       <c r="E95" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Unit of 4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ROSUVAS 10</t>
+          <t>PIOZ 15MG TAB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SIG1644A</t>
+          <t>48020714</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>23.062</v>
+        <v>78.52</v>
       </c>
       <c r="E96" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3882,35 +3882,35 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Strip of 15</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ROSUVAS 5</t>
+          <t>PIOZ MF-15 TAB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SIG1784A</t>
+          <t>28027440</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.125</v>
+        <v>14.592</v>
       </c>
       <c r="E97" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3918,35 +3918,35 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Strip of 15</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SHELCAL-500</t>
+          <t>ROSUVAS 10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>8LV2M362</t>
+          <t>SIG1644A</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>01/2028</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>9.91</v>
+        <v>23.062</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3965,24 +3965,24 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SHELCAL-500</t>
+          <t>ROSUVAS 5</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8LV2M447</t>
+          <t>SIG1784A</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>01/2028</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.89</v>
+        <v>13.125</v>
       </c>
       <c r="E99" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4006,16 +4006,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>8LVM349</t>
+          <t>8LV2M362</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>9.912000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -4037,24 +4037,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SHELCAL-CT</t>
+          <t>SHELCAL-500</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GAXF0023</t>
+          <t>8LV2M447</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>25.28</v>
+        <v>10.89</v>
       </c>
       <c r="E101" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4073,24 +4073,24 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SHELCAL-XT</t>
+          <t>SHELCAL-500</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2SG6M104</t>
+          <t>8LVM349</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>26.81</v>
+        <v>9.912000000000001</v>
       </c>
       <c r="E102" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4109,24 +4109,24 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SITARA M 100\500</t>
+          <t>SHELCAL-CT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EMV252758C</t>
+          <t>GAXF0023</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>16.383</v>
+        <v>25.28</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4134,23 +4134,23 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Strip of 15</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SITARA M 100\500</t>
+          <t>SHELCAL-XT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EMV252762</t>
+          <t>2SG6M104</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>16.383</v>
+        <v>26.81</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4170,35 +4170,35 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Strip of 15</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SITARA M 50/500</t>
+          <t>SITARA M 100\500</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EMV252263</t>
+          <t>EMV252758C</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>18.422</v>
+        <v>16.383</v>
       </c>
       <c r="E105" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SITARED M 50/500</t>
+          <t>SITARA M 100\500</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SIG2194A</t>
+          <t>EMV252762</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.75</v>
+        <v>16.383</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -4242,35 +4242,35 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Strip of 15</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SITARED M 50/500</t>
+          <t>SITARA M 50/500</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SIG2272B</t>
+          <t>EMV252263</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.75</v>
+        <v>18.422</v>
       </c>
       <c r="E107" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4278,35 +4278,35 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Strip of 15</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SITARED M XR 100/1000</t>
+          <t>SITARED M 50/500</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GTF1664B</t>
+          <t>SIG2194A</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>14.906</v>
+        <v>11.75</v>
       </c>
       <c r="E108" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -4314,35 +4314,35 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Strip of 15</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SITARED M XR 100/500</t>
+          <t>SITARED M 50/500</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AXC0097</t>
+          <t>SIG2272B</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>13.5</v>
+        <v>11.75</v>
       </c>
       <c r="E109" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4361,24 +4361,24 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SPORLAC-DS</t>
+          <t>SITARED M XR 100/1000</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BDS25019</t>
+          <t>GTF1664B</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>8.965999999999999</v>
+        <v>14.906</v>
       </c>
       <c r="E110" t="n">
-        <v>600</v>
+        <v>20</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4386,35 +4386,35 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Strip of 25</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STEMETIL-MD TAB</t>
+          <t>SITARED M XR 100/500</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SEA25022</t>
+          <t>AXC0097</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.87</v>
+        <v>13.5</v>
       </c>
       <c r="E111" t="n">
-        <v>279</v>
+        <v>90</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -4433,24 +4433,24 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SYSCAN-150</t>
+          <t>SPORLAC-DS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CBD2M001</t>
+          <t>BDS25019</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>20.17</v>
+        <v>8.965999999999999</v>
       </c>
       <c r="E112" t="n">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4458,71 +4458,71 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Strip of 1</t>
+          <t>Strip of 25</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>T-BACT OINT 5GM</t>
+          <t>STEMETIL-MD TAB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>K73K</t>
+          <t>SEA25022</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>108.36</v>
+        <v>11.87</v>
       </c>
       <c r="E113" t="n">
-        <v>5</v>
+        <v>279</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tube</t>
+          <t>Strip</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Tube of 1</t>
+          <t>Strip of 15</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TELMEKIND-TRIO 6.25 TAB</t>
+          <t>SYSCAN-150</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>A6OAY022</t>
+          <t>CBD2M001</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>01/2028</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>12.454</v>
+        <v>20.17</v>
       </c>
       <c r="E114" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4530,119 +4530,119 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Strip of 1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TELVOK-40 MG</t>
+          <t>T-BACT OINT 5GM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ATH2511142</t>
+          <t>K73K</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>7.097</v>
+        <v>108.36</v>
       </c>
       <c r="E115" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Tube</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Tube of 1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>THYRONORM 100</t>
+          <t>TELMEKIND-TRIO 6.25 TAB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TMH25237</t>
+          <t>A6OAY022</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>168.82</v>
+        <v>12.454</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bottle</t>
+          <t>Strip</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bottle of 1</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>THYRONORM 100</t>
+          <t>TELVOK-40 MG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TMN25217</t>
+          <t>ATH2511142</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>168.82</v>
+        <v>7.097</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bottle</t>
+          <t>Strip</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bottle of 1</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
@@ -4654,19 +4654,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TMH25258</t>
+          <t>TMH25237</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>11/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D118" t="n">
         <v>168.82</v>
       </c>
       <c r="E118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -4685,21 +4685,21 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>THYRONORM 112</t>
+          <t>THYRONORM 100</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TMI25008*</t>
+          <t>TMN25217</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>212.72</v>
+        <v>168.82</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -4721,12 +4721,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>THYRONORM 112</t>
+          <t>THYRONORM 100</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EBRH5005</t>
+          <t>TMH25258</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>251.7</v>
+        <v>168.82</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4757,21 +4757,21 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>THYRONORM 12.5</t>
+          <t>THYRONORM 112</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AEL0406*</t>
+          <t>TMI25008*</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>189.72</v>
+        <v>212.72</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -4793,24 +4793,24 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>THYRONORM 12.5</t>
+          <t>THYRONORM 112</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AEL0477</t>
+          <t>EBRH5005</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>11/2027</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>189.72</v>
+        <v>251.7</v>
       </c>
       <c r="E122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -4829,21 +4829,21 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>THYRONORM 125</t>
+          <t>THYRONORM 12.5</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EBRI5008</t>
+          <t>AEL0406*</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>216.63</v>
+        <v>189.72</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -4865,24 +4865,24 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>THYRONORM 125</t>
+          <t>THYRONORM 12.5</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EBRI5023</t>
+          <t>AEL0477</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>216.63</v>
+        <v>189.72</v>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4901,21 +4901,21 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>THYRONORM 25</t>
+          <t>THYRONORM 125</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TMB25278</t>
+          <t>EBRI5008</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>185.4</v>
+        <v>216.63</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -4937,12 +4937,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>THYRONORM 25</t>
+          <t>THYRONORM 125</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TMB25292</t>
+          <t>EBRI5023</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>185.4</v>
+        <v>216.63</v>
       </c>
       <c r="E126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -4973,21 +4973,21 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>THYRONORM 37.5</t>
+          <t>THYRONORM 25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TMC25063*</t>
+          <t>TMB25278</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>187.85</v>
+        <v>185.4</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -5009,12 +5009,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>THYRONORM 50</t>
+          <t>THYRONORM 25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TMD25396*</t>
+          <t>TMB25292</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>132.02</v>
+        <v>185.4</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -5045,24 +5045,24 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>THYRONORM 50</t>
+          <t>THYRONORM 37.5</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TMD25396</t>
+          <t>TMC25063*</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>132.02</v>
+        <v>187.85</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -5081,24 +5081,24 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>THYRONORM 62.5</t>
+          <t>THYRONORM 50</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EBRG5028*</t>
+          <t>TMD25396*</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>206.37</v>
+        <v>132.02</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -5117,24 +5117,24 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>THYRONORM 62.5</t>
+          <t>THYRONORM 50</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EBRF5036</t>
+          <t>TMD25396</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>206.37</v>
+        <v>132.02</v>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -5153,12 +5153,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>THYRONORM 75</t>
+          <t>THYRONORM 62.5</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TMF25182*</t>
+          <t>EBRG5028*</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>183.97</v>
+        <v>206.37</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -5189,24 +5189,24 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>THYRONORM 75</t>
+          <t>THYRONORM 62.5</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TMF25231</t>
+          <t>EBRF5036</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>183.97</v>
+        <v>206.37</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TMF25209</t>
+          <t>TMF25182*</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5261,21 +5261,21 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>THYRONORM 88</t>
+          <t>THYRONORM 75</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EBRG5028*</t>
+          <t>TMF25231</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>211.27</v>
+        <v>183.97</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -5297,24 +5297,24 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>THYRONORM 88</t>
+          <t>THYRONORM 75</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EBRG5036</t>
+          <t>TMF25209</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>211.28</v>
+        <v>183.97</v>
       </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -5333,96 +5333,96 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TRIGLYNASE-1</t>
+          <t>THYRONORM 88</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>28027170</t>
+          <t>EBRG5028*</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>02/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6.422</v>
+        <v>211.27</v>
       </c>
       <c r="E137" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Bottle</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Bottle of 1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TRIGLYNASE-2</t>
+          <t>THYRONORM 88</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>28027385</t>
+          <t>EBRG5036</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>04/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>9.352</v>
+        <v>211.28</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Bottle</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Bottle of 1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TRIGLYNASE-2</t>
+          <t>TRIGLYNASE-1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>28027306</t>
+          <t>28027170</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>03/2027</t>
+          <t>02/2027</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>9.352</v>
+        <v>6.422</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -5441,24 +5441,24 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TRIOLMEZEST 40 MG</t>
+          <t>TRIGLYNASE-2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GTC2880A</t>
+          <t>28027385</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>04/2027</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>21.844</v>
+        <v>9.352</v>
       </c>
       <c r="E140" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -5477,24 +5477,24 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TRYPTOMER-10 MG</t>
+          <t>TRIGLYNASE-2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>D2500387</t>
+          <t>28027306</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>03/2027</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2.546</v>
+        <v>9.352</v>
       </c>
       <c r="E141" t="n">
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -5502,35 +5502,35 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Strip of 30</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VSL 3 CAP</t>
+          <t>TRIOLMEZEST 40 MG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JMG1096A</t>
+          <t>GTC2880A</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>08/2027</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>45.51</v>
+        <v>21.844</v>
       </c>
       <c r="E142" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -5549,24 +5549,24 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>WONRIDE-M1</t>
+          <t>TRYPTOMER-10 MG</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>WNM1325004</t>
+          <t>D2500387</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>07/2027</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7.562</v>
+        <v>2.546</v>
       </c>
       <c r="E143" t="n">
-        <v>45</v>
+        <v>595</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -5574,35 +5574,35 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Strip of 15</t>
+          <t>Strip of 30</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>WONRIDE-M1</t>
+          <t>VSL 3 CAP</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>WNM1325005</t>
+          <t>JMG1096A</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>11/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>7.562</v>
+        <v>45.51</v>
       </c>
       <c r="E144" t="n">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -5610,35 +5610,35 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Strip of 15</t>
+          <t>Strip of 10</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>WONRIDE-M2</t>
+          <t>WONRIDE-M1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>WOH25004</t>
+          <t>WNM1325004</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>07/2027</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>8.593999999999999</v>
+        <v>7.562</v>
       </c>
       <c r="E145" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -5657,12 +5657,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>WONRIDE-M2</t>
+          <t>WONRIDE-M1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>WOH25005</t>
+          <t>WNM1325005</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>8.593999999999999</v>
+        <v>7.562</v>
       </c>
       <c r="E146" t="n">
         <v>180</v>
@@ -5693,96 +5693,96 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>XGLAR CART</t>
+          <t>WONRIDE-M2</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>C241GH4010</t>
+          <t>WOH25004</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>640.8</v>
+        <v>8.593999999999999</v>
       </c>
       <c r="E147" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Strip</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Unit of 1</t>
+          <t>Strip of 15</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>XSULIN R CART</t>
+          <t>WONRIDE-M2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TBB030225</t>
+          <t>WOH25005</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>01/2028</t>
+          <t>11/2027</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>175.1</v>
+        <v>8.593999999999999</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Strip</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Unit of 1</t>
+          <t>Strip of 15</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>XSULIN R CART</t>
+          <t>XGLAR CART</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>A042517604</t>
+          <t>C241GH4010</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>07/2028</t>
+          <t>06/2027</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>375.1</v>
+        <v>640.8</v>
       </c>
       <c r="E149" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -5801,24 +5801,24 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>XSULIN R VIAL</t>
+          <t>XSULIN R CART</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>A032515016</t>
+          <t>TBB030225</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>04/2027</t>
+          <t>01/2028</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>181.39</v>
+        <v>175.1</v>
       </c>
       <c r="E150" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -5837,24 +5837,24 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>YURPEAK 2.5MG/0.6ML PEN</t>
+          <t>XSULIN R CART</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>D921081</t>
+          <t>A042517604</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>05/2027</t>
+          <t>07/2028</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>13125</v>
+        <v>375.1</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -5873,28 +5873,28 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ZEDEX-SF COUGH SYP</t>
+          <t>XSULIN R VIAL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>D250569</t>
+          <t>A032515016</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>04/2027</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>190.31</v>
+        <v>181.39</v>
       </c>
       <c r="E152" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bottle</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -5902,35 +5902,35 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Bottle of 1</t>
+          <t>Unit of 1</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ZEDEX-SF COUGH SYP</t>
+          <t>YURPEAK 2.5MG/0.6ML PEN</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>D250570</t>
+          <t>D921081</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>05/2027</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>190.31</v>
+        <v>13125</v>
       </c>
       <c r="E153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bottle</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -5938,113 +5938,185 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bottle of 1</t>
+          <t>Unit of 1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ZERODOL-P</t>
+          <t>ZEDEX-SF COUGH SYP</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>KVB012511</t>
+          <t>D250569</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>08/2027</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>7.59</v>
+        <v>190.31</v>
       </c>
       <c r="E154" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Bottle</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Bottle of 1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ZERODOL-SP</t>
+          <t>ZEDEX-SF COUGH SYP</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FND082504</t>
+          <t>D250570</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>03/2028</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>13.96</v>
+        <v>190.31</v>
       </c>
       <c r="E155" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Bottle</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Strip of 10</t>
+          <t>Bottle of 1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t>ZERODOL-P</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>KVB012511</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>08/2027</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="E156" t="n">
+        <v>50</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>10</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ZERODOL-SP</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>FND082504</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>03/2028</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="E157" t="n">
+        <v>80</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>10</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Strip of 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>ZINCOVIT TAB</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>ZVT25220</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>02/2027</t>
         </is>
       </c>
-      <c r="D156" t="n">
+      <c r="D158" t="n">
         <v>7.179</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E158" t="n">
         <v>150</v>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Strip</t>
-        </is>
-      </c>
-      <c r="G156" t="n">
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Strip</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
         <v>15</v>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>Strip of 15</t>
         </is>
